--- a/tests/workbooktests/workbooks/test_inflation.xlsx
+++ b/tests/workbooktests/workbooks/test_inflation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7431B895-38DA-47B3-B54E-B4972BEDF1CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E1031B-F582-4293-9CBA-265D2DD7D76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
@@ -48,6 +48,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -2505,9 +2516,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2545,7 +2556,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2651,7 +2662,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2793,7 +2804,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3678,7 +3689,7 @@
       </c>
       <c r="B36" s="53">
         <f>_xll.qlCappedFlooredYoYInflationCouponEffectiveCap(B24,B24)</f>
-        <v>1.2461106238464053E-306</v>
+        <v>0</v>
       </c>
       <c r="C36" s="50">
         <f>_xll.qlCappedFlooredYoYInflationCouponEffectiveCap(C24,C24)</f>
@@ -3691,7 +3702,7 @@
       </c>
       <c r="B37" s="136">
         <f>_xll.qlCappedFlooredYoYInflationCouponEffectiveFloor(B24,B24)</f>
-        <v>1.3796170925349683E-306</v>
+        <v>0</v>
       </c>
       <c r="C37" s="201">
         <f>_xll.qlCappedFlooredYoYInflationCouponEffectiveFloor(C24,C24)</f>
@@ -7105,7 +7116,7 @@
       </c>
       <c r="B59" s="22" t="b">
         <f>ISERROR(_xll.qlInflationTermStructureSeasonality(B35,B35))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="22"/>
       <c r="D59" s="22" t="str">
@@ -7120,7 +7131,7 @@
       </c>
       <c r="B60" s="128" t="b">
         <f>_xll.qlInflationTermStructureHasSeasonality(B35,B35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="128"/>
       <c r="D60" s="128" t="b">
@@ -7887,7 +7898,7 @@
       </c>
       <c r="B48" s="74" t="b">
         <f>ISERROR(_xll.qlInflationTermStructureSeasonality(B21,B21))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="74"/>
       <c r="D48" s="74" t="str">
@@ -7902,7 +7913,7 @@
       </c>
       <c r="B49" s="52" t="b">
         <f>_xll.qlInflationTermStructureHasSeasonality(B21,B21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="52"/>
       <c r="D49" s="52" t="b">
@@ -8847,7 +8858,7 @@
       </c>
       <c r="B61" s="74" t="b">
         <f>ISERROR(_xll.qlInflationTermStructureSeasonality(B36,B36))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="74"/>
       <c r="D61" s="74" t="str">
@@ -8862,7 +8873,7 @@
       </c>
       <c r="B62" s="52" t="b">
         <f>_xll.qlInflationTermStructureHasSeasonality(B36,B36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="52"/>
       <c r="D62" s="52" t="b">
@@ -12480,12 +12491,12 @@
         <v>250</v>
       </c>
       <c r="B28" s="22" t="str">
-        <f>_xll.qlDiscountingSwapEngine(B27,,,,B27)</f>
-        <v>欣[test_inflation.xlsx]ZeroCouponInflationSwap!R28C2DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(B27,TRUE,,,B27)</f>
+        <v>欣[test_inflation.xlsx]ZeroCouponInflationSwap!R28C2DiscountingSwapEngine,C</v>
       </c>
       <c r="C28" s="57" t="str">
-        <f>_xll.qlDiscountingSwapEngine(C27,,,,C27)</f>
-        <v>欣[test_inflation.xlsx]ZeroCouponInflationSwap!R28C3DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(C27,TRUE,,,C27)</f>
+        <v>欣[test_inflation.xlsx]ZeroCouponInflationSwap!R28C3DiscountingSwapEngine,C</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -13052,12 +13063,12 @@
         <v>250</v>
       </c>
       <c r="B40" s="22" t="str">
-        <f>_xll.qlDiscountingSwapEngine(B39,,,,B39)</f>
-        <v>欣[test_inflation.xlsx]YoYInflationSwap!R40C2DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(B39,TRUE,,,B39)</f>
+        <v>欣[test_inflation.xlsx]YoYInflationSwap!R40C2DiscountingSwapEngine,C</v>
       </c>
       <c r="C40" s="22" t="str">
-        <f>_xll.qlDiscountingSwapEngine(C39,,,,C39)</f>
-        <v>欣[test_inflation.xlsx]YoYInflationSwap!R40C3DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(C39,TRUE,,,C39)</f>
+        <v>欣[test_inflation.xlsx]YoYInflationSwap!R40C3DiscountingSwapEngine,C</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -13711,12 +13722,12 @@
         <v>250</v>
       </c>
       <c r="B49" s="22" t="str">
-        <f>_xll.qlDiscountingSwapEngine(B48,,,,B48)</f>
-        <v>欣[test_inflation.xlsx]CPISwap!R49C2DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(B48,TRUE,,,B48)</f>
+        <v>欣[test_inflation.xlsx]CPISwap!R49C2DiscountingSwapEngine,C</v>
       </c>
       <c r="C49" s="57" t="str">
-        <f>_xll.qlDiscountingSwapEngine(C48,,,,C48)</f>
-        <v>欣[test_inflation.xlsx]CPISwap!R49C3DiscountingSwapEngine,A</v>
+        <f>_xll.qlDiscountingSwapEngine(C48,TRUE,,,C48)</f>
+        <v>欣[test_inflation.xlsx]CPISwap!R49C3DiscountingSwapEngine,C</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
